--- a/Tests/Validation/Wheat/data/FAR TAS W16-06.xlsx
+++ b/Tests/Validation/Wheat/data/FAR TAS W16-06.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,141 +430,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA149"/>
+  <dimension ref="A1:W149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Seeds</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population.se</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population.se</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Height</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Height.se</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation.se</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -563,52 +556,34 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>200</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,44 +591,30 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>200</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
         <v>0.85375</v>
       </c>
-      <c r="I3" t="n">
+      <c r="E3" t="n">
         <v>0.314576434802949</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>241.583333333333</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.653250419908867</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>241.583333333333</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.653250419908867</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -662,10 +623,6 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,34 +630,20 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="I4" t="n">
+      <c r="E4" t="n">
         <v>0.957427107756338</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -715,10 +658,6 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -726,34 +665,20 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
         <v>0.8675</v>
       </c>
-      <c r="I5" t="n">
+      <c r="E5" t="n">
         <v>0.478713553878169</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -768,10 +693,6 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -779,44 +700,30 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
         <v>0.86375</v>
       </c>
-      <c r="I6" t="n">
+      <c r="E6" t="n">
         <v>0.125</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>561.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.77679317234432</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>561.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.77679317234432</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -825,10 +732,6 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -836,34 +739,20 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
         <v>0.83</v>
       </c>
-      <c r="I7" t="n">
+      <c r="E7" t="n">
         <v>0.408248290463863</v>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -878,10 +767,6 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -889,44 +774,30 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
         <v>0.8075</v>
       </c>
-      <c r="I8" t="n">
+      <c r="E8" t="n">
         <v>0.629152869605896</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>764.583333333333</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.13320056411852</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>764.583333333333</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.13320056411852</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -935,10 +806,6 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -946,34 +813,20 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>200</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
         <v>0.7725</v>
       </c>
-      <c r="I9" t="n">
+      <c r="E9" t="n">
         <v>0.75</v>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -988,10 +841,6 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -999,44 +848,30 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>200</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
         <v>0.7175</v>
       </c>
-      <c r="I10" t="n">
+      <c r="E10" t="n">
         <v>1.25</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>986.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.17531516655778</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>986.25</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.17531516655778</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1045,10 +880,6 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1056,36 +887,22 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>200</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>2291.11996598044</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.00482705656298</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>2291.11996598044</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.00482705656298</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1098,10 +915,6 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1109,34 +922,20 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>200</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
         <v>0.60625</v>
       </c>
-      <c r="I12" t="n">
+      <c r="E12" t="n">
         <v>2.05522707585642</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1151,10 +950,6 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1162,7 +957,7 @@
           <t>FAR TAS W16-06PGRSingleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1170,62 +965,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>200</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SingleMid</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>76.67400000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.27889692052696</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12.2333333333333</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.066666666666667</v>
+      </c>
       <c r="R13" t="n">
-        <v>76.67400000000001</v>
+        <v>10.2333333333333</v>
       </c>
       <c r="S13" t="n">
-        <v>1.27889692052696</v>
+        <v>0.20275875100994</v>
       </c>
       <c r="T13" t="n">
-        <v>12.2333333333333</v>
+        <v>2.36410484913894</v>
       </c>
       <c r="U13" t="n">
-        <v>0.066666666666667</v>
+        <v>0.398211576502728</v>
       </c>
       <c r="V13" t="n">
-        <v>10.2333333333333</v>
+        <v>1072.25331159777</v>
       </c>
       <c r="W13" t="n">
-        <v>0.20275875100994</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.36410484913894</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.398211576502728</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1072.25331159777</v>
-      </c>
-      <c r="AA13" t="n">
         <v>0.319681384243743</v>
       </c>
     </row>
@@ -1235,52 +1012,34 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>200</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>443.75</v>
+      </c>
+      <c r="M14" t="n">
+        <v>443.75</v>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>443.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>443.75</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1288,44 +1047,30 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>200</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
         <v>0.8525</v>
       </c>
-      <c r="I15" t="n">
+      <c r="E15" t="n">
         <v>0.322748612183951</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>212.916666666667</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.229885237068896</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>212.916666666667</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.229885237068896</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1334,10 +1079,6 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1345,34 +1086,20 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>200</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
         <v>0.7925</v>
       </c>
-      <c r="I16" t="n">
+      <c r="E16" t="n">
         <v>0.478713553878168</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1387,10 +1114,6 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1398,34 +1121,20 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>200</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
         <v>0.85</v>
       </c>
-      <c r="I17" t="n">
+      <c r="E17" t="n">
         <v>0.408248290463863</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1440,10 +1149,6 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1451,44 +1156,30 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>200</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
         <v>0.85125</v>
       </c>
-      <c r="I18" t="n">
+      <c r="E18" t="n">
         <v>0.239356776939085</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.63391343821318</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>427.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.63391343821318</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1497,10 +1188,6 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1508,34 +1195,20 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>200</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
         <v>0.82</v>
       </c>
-      <c r="I19" t="n">
+      <c r="E19" t="n">
         <v>0.408248290463863</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1550,10 +1223,6 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1561,44 +1230,30 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>200</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
         <v>0.8075</v>
       </c>
-      <c r="I20" t="n">
+      <c r="E20" t="n">
         <v>0.478713553878169</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>616.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.03257613405765</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>616.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.03257613405765</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1607,10 +1262,6 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1618,34 +1269,20 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>200</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
         <v>0.7825</v>
       </c>
-      <c r="I21" t="n">
+      <c r="E21" t="n">
         <v>1.31497781983829</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1660,10 +1297,6 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1671,44 +1304,30 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>200</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
         <v>0.72</v>
       </c>
-      <c r="I22" t="n">
+      <c r="E22" t="n">
         <v>0.707106781186548</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>886.666666666667</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.720082299823095</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>886.666666666667</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.720082299823095</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1717,10 +1336,6 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1728,36 +1343,22 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
-        <v>200</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>2129.69837316856</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.37125972247466</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>2129.69837316856</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.37125972247466</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1770,10 +1371,6 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1781,34 +1378,20 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>200</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
         <v>0.59375</v>
       </c>
-      <c r="I24" t="n">
+      <c r="E24" t="n">
         <v>1.10632650394598</v>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1823,10 +1406,6 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1834,7 +1413,7 @@
           <t>FAR TAS W16-06PGRDoubleMidSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1842,62 +1421,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>200</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>DoubleMid</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>76.2806666666667</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.99045734554761</v>
+      </c>
+      <c r="P25" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.251661147842358</v>
+      </c>
       <c r="R25" t="n">
-        <v>76.2806666666667</v>
+        <v>10.6333333333333</v>
       </c>
       <c r="S25" t="n">
-        <v>1.99045734554761</v>
+        <v>0.240370085030932</v>
       </c>
       <c r="T25" t="n">
-        <v>12.7</v>
+        <v>2.26611280736052</v>
       </c>
       <c r="U25" t="n">
-        <v>0.251661147842358</v>
+        <v>0.237222906741652</v>
       </c>
       <c r="V25" t="n">
-        <v>10.6333333333333</v>
+        <v>1133.1856932597</v>
       </c>
       <c r="W25" t="n">
-        <v>0.240370085030932</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.26611280736052</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.237222906741652</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1133.1856932597</v>
-      </c>
-      <c r="AA25" t="n">
         <v>0.301018383656337</v>
       </c>
     </row>
@@ -1907,52 +1468,34 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
-        <v>200</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>385</v>
+      </c>
+      <c r="M26" t="n">
+        <v>385</v>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>385</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>385</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1960,44 +1503,30 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>200</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
         <v>0.8275</v>
       </c>
-      <c r="I27" t="n">
+      <c r="E27" t="n">
         <v>1.16368667031408</v>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>200.416666666667</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.51861192941672</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>200.416666666667</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.51861192941672</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -2006,10 +1535,6 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2017,34 +1542,20 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>200</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
         <v>0.7825</v>
       </c>
-      <c r="I28" t="n">
+      <c r="E28" t="n">
         <v>0.8539125638299661</v>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2059,10 +1570,6 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2070,34 +1577,20 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>200</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
         <v>0.8774999999999999</v>
       </c>
-      <c r="I29" t="n">
+      <c r="E29" t="n">
         <v>0.249999999999999</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2112,10 +1605,6 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2123,44 +1612,30 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>200</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
         <v>0.86875</v>
       </c>
-      <c r="I30" t="n">
+      <c r="E30" t="n">
         <v>0.239356776939085</v>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>553.75</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.34435548374181</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>553.75</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.34435548374181</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2169,10 +1644,6 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2180,34 +1651,20 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>200</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
         <v>0.845</v>
       </c>
-      <c r="I31" t="n">
+      <c r="E31" t="n">
         <v>0.288675134594813</v>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2222,10 +1679,6 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2233,44 +1686,30 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>200</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
         <v>0.8375</v>
       </c>
-      <c r="I32" t="n">
+      <c r="E32" t="n">
         <v>0.25</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>784.166666666667</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.57130455003342</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>784.166666666667</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.57130455003342</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2279,10 +1718,6 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2290,34 +1725,20 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>200</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
         <v>0.78</v>
       </c>
-      <c r="I33" t="n">
+      <c r="E33" t="n">
         <v>1.35400640077266</v>
       </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2332,10 +1753,6 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2343,44 +1760,30 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>200</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
         <v>0.745</v>
       </c>
-      <c r="I34" t="n">
+      <c r="E34" t="n">
         <v>0.500000000000001</v>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>1017.08333333333</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.570797849667626</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>1017.08333333333</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.570797849667626</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2389,10 +1792,6 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2400,36 +1799,22 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
-        <v>200</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>2378.43732881513</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.18846387529691</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>2378.43732881513</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.18846387529691</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -2442,10 +1827,6 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2453,34 +1834,20 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>200</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
         <v>0.62</v>
       </c>
-      <c r="I36" t="n">
+      <c r="E36" t="n">
         <v>0.353553390593274</v>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2495,10 +1862,6 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2506,7 +1869,7 @@
           <t>FAR TAS W16-06PGREarly1Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2514,62 +1877,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>200</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Early1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>75.9733333333333</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.63651795820001</v>
+      </c>
+      <c r="P37" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.0577350269189628</v>
+      </c>
       <c r="R37" t="n">
-        <v>75.9733333333333</v>
+        <v>11.2</v>
       </c>
       <c r="S37" t="n">
-        <v>0.63651795820001</v>
+        <v>0.1</v>
       </c>
       <c r="T37" t="n">
-        <v>12.3</v>
+        <v>2.12511160702432</v>
       </c>
       <c r="U37" t="n">
-        <v>0.0577350269189628</v>
+        <v>0.128807615965335</v>
       </c>
       <c r="V37" t="n">
-        <v>11.2</v>
+        <v>944.041151757072</v>
       </c>
       <c r="W37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.12511160702432</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.128807615965335</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>944.041151757072</v>
-      </c>
-      <c r="AA37" t="n">
         <v>0.4861395064498</v>
       </c>
     </row>
@@ -2579,52 +1924,34 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="n">
-        <v>200</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2632,44 +1959,30 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>200</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
         <v>0.8375</v>
       </c>
-      <c r="I39" t="n">
+      <c r="E39" t="n">
         <v>0.777281587757401</v>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>222</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.728265315918841</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>222</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.728265315918841</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2678,10 +1991,6 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2689,34 +1998,20 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>200</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
         <v>0.8025</v>
       </c>
-      <c r="I40" t="n">
+      <c r="E40" t="n">
         <v>1.03077640640442</v>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2731,10 +2026,6 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2742,34 +2033,20 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>200</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
         <v>0.8774999999999999</v>
       </c>
-      <c r="I41" t="n">
+      <c r="E41" t="n">
         <v>0.249999999999999</v>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2784,10 +2061,6 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2795,44 +2068,30 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>200</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
         <v>0.86875</v>
       </c>
-      <c r="I42" t="n">
+      <c r="E42" t="n">
         <v>0.375</v>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>555</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.30703226177984</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>555</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.30703226177984</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2841,10 +2100,6 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2852,34 +2107,20 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>200</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
         <v>0.855</v>
       </c>
-      <c r="I43" t="n">
+      <c r="E43" t="n">
         <v>0.5</v>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2894,10 +2135,6 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2905,44 +2142,30 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>200</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
         <v>0.83</v>
       </c>
-      <c r="I44" t="n">
+      <c r="E44" t="n">
         <v>0.408248290463863</v>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>815</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.42886901662352</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>815</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.42886901662352</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2951,10 +2174,6 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2962,34 +2181,20 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>200</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
         <v>0.7775</v>
       </c>
-      <c r="I45" t="n">
+      <c r="E45" t="n">
         <v>2.39356776939085</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -3004,10 +2209,6 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3015,44 +2216,30 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>200</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
         <v>0.7325</v>
       </c>
-      <c r="I46" t="n">
+      <c r="E46" t="n">
         <v>1.10867789130417</v>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>1026.66666666667</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.06066017177982</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>1026.66666666667</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.06066017177982</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3061,10 +2248,6 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3072,36 +2255,22 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="n">
-        <v>200</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>1917.27429298843</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.80200339616147</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
-        <v>1917.27429298843</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1.80200339616147</v>
-      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -3114,10 +2283,6 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3125,34 +2290,20 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>200</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
         <v>0.61125</v>
       </c>
-      <c r="I48" t="n">
+      <c r="E48" t="n">
         <v>1.7838978857173</v>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3167,10 +2318,6 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3178,7 +2325,7 @@
           <t>FAR TAS W16-06PGREarly2Seeds200CvManning</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -3186,62 +2333,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>200</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Early2</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>76.28466666666669</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.878342631196836</v>
+      </c>
+      <c r="P49" t="n">
+        <v>12.6333333333333</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.338296385503074</v>
+      </c>
       <c r="R49" t="n">
-        <v>76.28466666666669</v>
+        <v>10.7333333333333</v>
       </c>
       <c r="S49" t="n">
-        <v>0.878342631196836</v>
+        <v>0.17638342073764</v>
       </c>
       <c r="T49" t="n">
-        <v>12.6333333333333</v>
+        <v>2.31503921272472</v>
       </c>
       <c r="U49" t="n">
-        <v>0.338296385503074</v>
+        <v>0.08128953334890759</v>
       </c>
       <c r="V49" t="n">
-        <v>10.7333333333333</v>
+        <v>974.113733504666</v>
       </c>
       <c r="W49" t="n">
-        <v>0.17638342073764</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.31503921272472</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0.08128953334890759</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>974.113733504666</v>
-      </c>
-      <c r="AA49" t="n">
         <v>0.0709073504761331</v>
       </c>
     </row>
@@ -3251,52 +2380,34 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="n">
-        <v>200</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>408.75</v>
+      </c>
+      <c r="M50" t="n">
+        <v>408.75</v>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="n">
-        <v>408.75</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>408.75</v>
-      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3304,44 +2415,30 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>200</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
         <v>0.83625</v>
       </c>
-      <c r="I51" t="n">
+      <c r="E51" t="n">
         <v>0.773923984208613</v>
       </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>211.75</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.596032406526382</v>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
-        <v>211.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0.596032406526382</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3350,10 +2447,6 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3361,34 +2454,20 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>200</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
         <v>0.77</v>
       </c>
-      <c r="I52" t="n">
+      <c r="E52" t="n">
         <v>1.08012344973464</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3403,10 +2482,6 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3414,34 +2489,20 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>200</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
         <v>0.8575</v>
       </c>
-      <c r="I53" t="n">
+      <c r="E53" t="n">
         <v>0.250000000000001</v>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3456,10 +2517,6 @@
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3467,44 +2524,30 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>200</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
         <v>0.86125</v>
       </c>
-      <c r="I54" t="n">
+      <c r="E54" t="n">
         <v>0.314576434802948</v>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>506.25</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.554338945652086</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>506.25</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0.554338945652086</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -3513,10 +2556,6 @@
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3524,34 +2563,20 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>200</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
         <v>0.83</v>
       </c>
-      <c r="I55" t="n">
+      <c r="E55" t="n">
         <v>0.577350269189625</v>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3566,10 +2591,6 @@
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3577,44 +2598,30 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>200</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
         <v>0.8125</v>
       </c>
-      <c r="I56" t="n">
+      <c r="E56" t="n">
         <v>0.478713553878169</v>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>727.916666666667</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.60781511513123</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>727.916666666667</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.60781511513123</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3623,10 +2630,6 @@
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3634,34 +2637,20 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>200</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
         <v>0.7524999999999999</v>
       </c>
-      <c r="I57" t="n">
+      <c r="E57" t="n">
         <v>2.09662427090152</v>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3676,10 +2665,6 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3687,44 +2672,30 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>200</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
         <v>0.72</v>
       </c>
-      <c r="I58" t="n">
+      <c r="E58" t="n">
         <v>1.47196014438797</v>
       </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>969.583333333333</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.29881534341734</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>969.583333333333</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1.29881534341734</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3733,10 +2704,6 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3744,36 +2711,22 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="n">
-        <v>200</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>2248.83604740075</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.02928946776297</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>2248.83604740075</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1.02928946776297</v>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -3786,10 +2739,6 @@
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3797,34 +2746,20 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>200</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
         <v>0.6125</v>
       </c>
-      <c r="I60" t="n">
+      <c r="E60" t="n">
         <v>1.19895788082818</v>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3839,10 +2774,6 @@
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3850,7 +2781,7 @@
           <t>FAR TAS W16-06PGRTripleEarlySeeds200CvManning</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -3858,62 +2789,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>200</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>TripleEarly</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>75.14400000000001</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.71015593830894</v>
+      </c>
+      <c r="P61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.416333199893226</v>
+      </c>
       <c r="R61" t="n">
-        <v>75.14400000000001</v>
+        <v>10.5666666666667</v>
       </c>
       <c r="S61" t="n">
-        <v>1.71015593830894</v>
+        <v>0.202758751009941</v>
       </c>
       <c r="T61" t="n">
-        <v>12.5</v>
+        <v>2.56962269359558</v>
       </c>
       <c r="U61" t="n">
-        <v>0.416333199893226</v>
+        <v>0.204419395332601</v>
       </c>
       <c r="V61" t="n">
-        <v>10.5666666666667</v>
+        <v>1051.16437577464</v>
       </c>
       <c r="W61" t="n">
-        <v>0.202758751009941</v>
-      </c>
-      <c r="X61" t="n">
-        <v>2.56962269359558</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0.204419395332601</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1051.16437577464</v>
-      </c>
-      <c r="AA61" t="n">
         <v>0.303702669431667</v>
       </c>
     </row>
@@ -3923,52 +2836,34 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="n">
-        <v>200</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>525</v>
+      </c>
+      <c r="M62" t="n">
+        <v>525</v>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>525</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>525</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3976,44 +2871,30 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>200</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
         <v>0.85375</v>
       </c>
-      <c r="I63" t="n">
+      <c r="E63" t="n">
         <v>0.850857410694256</v>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>241.75</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.745775137394348</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="n">
-        <v>241.75</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0.745775137394348</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -4022,10 +2903,6 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4033,34 +2910,20 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>200</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="I64" t="n">
+      <c r="E64" t="n">
         <v>0.645497224367903</v>
       </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
@@ -4075,10 +2938,6 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4086,34 +2945,20 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>200</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
         <v>0.87</v>
       </c>
-      <c r="I65" t="n">
+      <c r="E65" t="n">
         <v>0.408248290463863</v>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -4128,10 +2973,6 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4139,44 +2980,30 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>200</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
         <v>0.865</v>
       </c>
-      <c r="I66" t="n">
+      <c r="E66" t="n">
         <v>0.204124145231932</v>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>532.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2.47066118006227</v>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>532.5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2.47066118006227</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4185,10 +3012,6 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4196,34 +3019,20 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>200</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
         <v>0.835</v>
       </c>
-      <c r="I67" t="n">
+      <c r="E67" t="n">
         <v>0.288675134594814</v>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
@@ -4238,10 +3047,6 @@
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4249,44 +3054,30 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>200</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="I68" t="n">
+      <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>770.833333333333</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2.81324578589426</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
-        <v>770.833333333333</v>
-      </c>
-      <c r="O68" t="n">
-        <v>2.81324578589426</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4295,10 +3086,6 @@
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4306,34 +3093,20 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>200</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
         <v>0.7475000000000001</v>
       </c>
-      <c r="I69" t="n">
+      <c r="E69" t="n">
         <v>2.01556443707464</v>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
@@ -4348,10 +3121,6 @@
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4359,44 +3128,30 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>200</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
         <v>0.7125</v>
       </c>
-      <c r="I70" t="n">
+      <c r="E70" t="n">
         <v>1.10867789130417</v>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>987.083333333333</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1.60493307810176</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
-        <v>987.083333333333</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1.60493307810176</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4405,10 +3160,6 @@
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4416,36 +3167,22 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="n">
-        <v>200</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>2335.55415054475</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.34753881760868</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="n">
-        <v>2335.55415054475</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1.34753881760868</v>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -4458,10 +3195,6 @@
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4469,34 +3202,20 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>200</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
         <v>0.6025</v>
       </c>
-      <c r="I72" t="n">
+      <c r="E72" t="n">
         <v>0.25</v>
       </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -4511,10 +3230,6 @@
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4522,7 +3237,7 @@
           <t>FAR TAS W16-06PGRDoubleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -4530,62 +3245,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>200</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>DoubleLate</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>76.7346666666667</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.634671918745779</v>
+      </c>
+      <c r="P73" t="n">
+        <v>12.5666666666667</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.266666666666666</v>
+      </c>
       <c r="R73" t="n">
-        <v>76.7346666666667</v>
+        <v>10.6666666666667</v>
       </c>
       <c r="S73" t="n">
-        <v>0.634671918745779</v>
+        <v>0.120185042515466</v>
       </c>
       <c r="T73" t="n">
-        <v>12.5666666666667</v>
+        <v>2.01636664947386</v>
       </c>
       <c r="U73" t="n">
-        <v>0.266666666666666</v>
+        <v>0.235928158469177</v>
       </c>
       <c r="V73" t="n">
-        <v>10.6666666666667</v>
+        <v>1013.69585474993</v>
       </c>
       <c r="W73" t="n">
-        <v>0.120185042515466</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2.01636664947386</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0.235928158469177</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>1013.69585474993</v>
-      </c>
-      <c r="AA73" t="n">
         <v>0.728621345313392</v>
       </c>
     </row>
@@ -4595,52 +3292,34 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="n">
-        <v>200</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4648,44 +3327,30 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>200</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
         <v>0.8425</v>
       </c>
-      <c r="I75" t="n">
+      <c r="E75" t="n">
         <v>0.5951190357119041</v>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>224.75</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.295764859055046</v>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="n">
-        <v>224.75</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0.295764859055046</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -4694,10 +3359,6 @@
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4705,34 +3366,20 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>200</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
         <v>0.8025</v>
       </c>
-      <c r="I76" t="n">
+      <c r="E76" t="n">
         <v>1.54784796841723</v>
       </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -4747,10 +3394,6 @@
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4758,34 +3401,20 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>200</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
         <v>0.8525</v>
       </c>
-      <c r="I77" t="n">
+      <c r="E77" t="n">
         <v>0.249999999999999</v>
       </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
@@ -4800,10 +3429,6 @@
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4811,44 +3436,30 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>200</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
         <v>0.85875</v>
       </c>
-      <c r="I78" t="n">
+      <c r="E78" t="n">
         <v>0.473242362150022</v>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>442.625</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.97646306568071</v>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>442.625</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1.97646306568071</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -4857,10 +3468,6 @@
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4868,34 +3475,20 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>200</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
         <v>0.825</v>
       </c>
-      <c r="I79" t="n">
+      <c r="E79" t="n">
         <v>0.866025403784438</v>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -4910,10 +3503,6 @@
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4921,44 +3510,30 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>200</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="I80" t="n">
+      <c r="E80" t="n">
         <v>1.5545631755148</v>
       </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>635</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1.52145154862546</v>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="n">
-        <v>635</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1.52145154862546</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4967,10 +3542,6 @@
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4978,34 +3549,20 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>200</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
         <v>0.7825</v>
       </c>
-      <c r="I81" t="n">
+      <c r="E81" t="n">
         <v>1.18145390656315</v>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
@@ -5020,10 +3577,6 @@
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5031,44 +3584,30 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>200</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
         <v>0.715</v>
       </c>
-      <c r="I82" t="n">
+      <c r="E82" t="n">
         <v>1.84842275106824</v>
       </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>928.75</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1.23860547331203</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="n">
-        <v>928.75</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1.23860547331203</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -5077,10 +3616,6 @@
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5088,36 +3623,22 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="n">
-        <v>200</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>2051.62081253756</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1.14807577506268</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="n">
-        <v>2051.62081253756</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1.14807577506268</v>
-      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
@@ -5130,10 +3651,6 @@
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5141,34 +3658,20 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>200</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
         <v>0.6</v>
       </c>
-      <c r="I84" t="n">
+      <c r="E84" t="n">
         <v>1.24163870214595</v>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
@@ -5183,10 +3686,6 @@
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5194,7 +3693,7 @@
           <t>FAR TAS W16-06PGRTripleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -5202,62 +3701,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>200</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>TripleLate</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>77.4146666666667</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.316736132731607</v>
+      </c>
+      <c r="P85" t="n">
+        <v>12.4666666666667</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.0881917103688197</v>
+      </c>
       <c r="R85" t="n">
-        <v>77.4146666666667</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S85" t="n">
-        <v>0.316736132731607</v>
+        <v>0.1</v>
       </c>
       <c r="T85" t="n">
-        <v>12.4666666666667</v>
+        <v>2.37918619294294</v>
       </c>
       <c r="U85" t="n">
-        <v>0.0881917103688197</v>
+        <v>0.0802535878997693</v>
       </c>
       <c r="V85" t="n">
-        <v>9.800000000000001</v>
+        <v>1155.7273986585</v>
       </c>
       <c r="W85" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X85" t="n">
-        <v>2.37918619294294</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0.0802535878997693</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1155.7273986585</v>
-      </c>
-      <c r="AA85" t="n">
         <v>0.210516487332766</v>
       </c>
     </row>
@@ -5267,52 +3748,34 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="n">
-        <v>200</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="M86" t="n">
+        <v>257.5</v>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="n">
-        <v>257.5</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>257.5</v>
-      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5320,44 +3783,30 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>200</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
         <v>0.85375</v>
       </c>
-      <c r="I87" t="n">
+      <c r="E87" t="n">
         <v>0.473242362150022</v>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>242.416666666667</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.997995676528897</v>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="n">
-        <v>242.416666666667</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0.997995676528897</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -5366,10 +3815,6 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5377,34 +3822,20 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>200</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
         <v>0.835</v>
       </c>
-      <c r="I88" t="n">
+      <c r="E88" t="n">
         <v>0.288675134594813</v>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
@@ -5419,10 +3850,6 @@
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5430,34 +3857,20 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>200</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
         <v>0.88</v>
       </c>
-      <c r="I89" t="n">
+      <c r="E89" t="n">
         <v>0</v>
       </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -5472,10 +3885,6 @@
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5483,44 +3892,30 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>200</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
         <v>0.875</v>
       </c>
-      <c r="I90" t="n">
+      <c r="E90" t="n">
         <v>0</v>
       </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>607.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.82915619758885</v>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="n">
-        <v>607.5</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0.82915619758885</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5529,10 +3924,6 @@
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5540,34 +3931,20 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>200</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
         <v>0.8525</v>
       </c>
-      <c r="I91" t="n">
+      <c r="E91" t="n">
         <v>0.249999999999999</v>
       </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
@@ -5582,10 +3959,6 @@
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5593,44 +3966,30 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>200</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
         <v>0.825</v>
       </c>
-      <c r="I92" t="n">
+      <c r="E92" t="n">
         <v>0.288675134594813</v>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>813.75</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.442922742197277</v>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="n">
-        <v>813.75</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0.442922742197277</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5639,10 +3998,6 @@
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5650,34 +4005,20 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>200</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
         <v>0.7725</v>
       </c>
-      <c r="I93" t="n">
+      <c r="E93" t="n">
         <v>0.8539125638299661</v>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
@@ -5692,10 +4033,6 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5703,44 +4040,30 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>200</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
         <v>0.7375</v>
       </c>
-      <c r="I94" t="n">
+      <c r="E94" t="n">
         <v>1.10867789130417</v>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>999.583333333333</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.688446318410762</v>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="n">
-        <v>999.583333333333</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0.688446318410762</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -5749,10 +4072,6 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5760,36 +4079,22 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="n">
-        <v>200</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>2314.05731324651</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.46755339413039</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="n">
-        <v>2314.05731324651</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1.46755339413039</v>
-      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -5802,10 +4107,6 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5813,34 +4114,20 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>200</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
         <v>0.60125</v>
       </c>
-      <c r="I96" t="n">
+      <c r="E96" t="n">
         <v>0.657488909919146</v>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -5855,10 +4142,6 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5866,7 +4149,7 @@
           <t>FAR TAS W16-06PGRSingleLateSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -5874,62 +4157,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>200</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>SingleLate</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>75.2106666666667</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1.140403632248</v>
+      </c>
+      <c r="P97" t="n">
+        <v>12.7333333333333</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.260341655863555</v>
+      </c>
       <c r="R97" t="n">
-        <v>75.2106666666667</v>
+        <v>10.3666666666667</v>
       </c>
       <c r="S97" t="n">
-        <v>1.140403632248</v>
+        <v>0.0881917103688194</v>
       </c>
       <c r="T97" t="n">
-        <v>12.7333333333333</v>
+        <v>2.03758861249179</v>
       </c>
       <c r="U97" t="n">
-        <v>0.260341655863555</v>
+        <v>0.336517222928792</v>
       </c>
       <c r="V97" t="n">
-        <v>10.3666666666667</v>
+        <v>1011.23932246099</v>
       </c>
       <c r="W97" t="n">
-        <v>0.0881917103688194</v>
-      </c>
-      <c r="X97" t="n">
-        <v>2.03758861249179</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>0.336517222928792</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>1011.23932246099</v>
-      </c>
-      <c r="AA97" t="n">
         <v>0.155537867151348</v>
       </c>
     </row>
@@ -5939,38 +4204,28 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>42508</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>50</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+        <v>0.3425</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.00478713553878169</v>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0.3425</v>
+        <v>49.375</v>
       </c>
       <c r="I98" t="n">
-        <v>0.00478713553878169</v>
+        <v>6.07033428513894</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="n">
-        <v>49.375</v>
-      </c>
-      <c r="M98" t="n">
-        <v>6.07033428513894</v>
-      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
@@ -5981,10 +4236,6 @@
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5992,48 +4243,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="n">
-        <v>50</v>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>795</v>
+      </c>
+      <c r="M99" t="n">
+        <v>132.5</v>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="n">
-        <v>795</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>132.5</v>
-      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6041,44 +4278,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>50</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
         <v>0.82625</v>
       </c>
-      <c r="I100" t="n">
+      <c r="E100" t="n">
         <v>1.14336856116769</v>
       </c>
+      <c r="F100" t="n">
+        <v>564.85939518252</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.357039423612041</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
-        <v>564.85939518252</v>
+        <v>221.416666666667</v>
       </c>
       <c r="K100" t="n">
-        <v>0.357039423612041</v>
+        <v>0.682367203197809</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="n">
-        <v>221.416666666667</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0.682367203197809</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -6087,10 +4314,6 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6098,30 +4321,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>50</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H101" t="n">
         <v>0.79</v>
       </c>
-      <c r="I101" t="n">
+      <c r="E101" t="n">
         <v>1.47196014438797</v>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
@@ -6136,10 +4349,6 @@
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6147,30 +4356,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>50</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H102" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="I102" t="n">
+      <c r="E102" t="n">
         <v>0.250000000000001</v>
       </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -6185,10 +4384,6 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6196,40 +4391,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>50</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H103" t="n">
         <v>0.86625</v>
       </c>
-      <c r="I103" t="n">
+      <c r="E103" t="n">
         <v>0.239356776939084</v>
       </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>583.75</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1.90804219030922</v>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="n">
-        <v>583.75</v>
-      </c>
-      <c r="O103" t="n">
-        <v>1.90804219030922</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
@@ -6238,10 +4423,6 @@
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6249,30 +4430,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>50</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H104" t="n">
         <v>0.8375</v>
       </c>
-      <c r="I104" t="n">
+      <c r="E104" t="n">
         <v>0.629152869605895</v>
       </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -6287,10 +4458,6 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6298,40 +4465,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>50</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H105" t="n">
         <v>0.82</v>
       </c>
-      <c r="I105" t="n">
+      <c r="E105" t="n">
         <v>1.08012344973464</v>
       </c>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="n">
+        <v>822.083333333333</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1.49284559247196</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="n">
-        <v>822.083333333333</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1.49284559247196</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
@@ -6340,10 +4497,6 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6351,30 +4504,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>50</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H106" t="n">
         <v>0.7875</v>
       </c>
-      <c r="I106" t="n">
+      <c r="E106" t="n">
         <v>1.10867789130417</v>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
@@ -6389,10 +4532,6 @@
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6400,40 +4539,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>50</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H107" t="n">
         <v>0.7225</v>
       </c>
-      <c r="I107" t="n">
+      <c r="E107" t="n">
         <v>1.60078105935821</v>
       </c>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="n">
+        <v>1024.16666666667</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.657928849018164</v>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="n">
-        <v>1024.16666666667</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0.657928849018164</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
@@ -6442,10 +4571,6 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6453,32 +4578,22 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="n">
-        <v>50</v>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="F108" t="n">
+        <v>2258.60221383582</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.57810997374132</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="n">
-        <v>2258.60221383582</v>
-      </c>
-      <c r="K108" t="n">
-        <v>1.57810997374132</v>
-      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -6491,10 +4606,6 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6502,30 +4613,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>50</v>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
         <v>0.59875</v>
       </c>
-      <c r="I109" t="n">
+      <c r="E109" t="n">
         <v>1.96187622783226</v>
       </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
@@ -6540,10 +4641,6 @@
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6551,7 +4648,7 @@
           <t>FAR TAS W16-06PGRNoneSeeds50CvManning</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -6559,58 +4656,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>50</v>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>77.5653333333333</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1.54437056577897</v>
+      </c>
+      <c r="P110" t="n">
+        <v>12.3666666666667</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.272845092395748</v>
+      </c>
       <c r="R110" t="n">
-        <v>77.5653333333333</v>
+        <v>10.6333333333333</v>
       </c>
       <c r="S110" t="n">
-        <v>1.54437056577897</v>
+        <v>0.352766841475279</v>
       </c>
       <c r="T110" t="n">
-        <v>12.3666666666667</v>
+        <v>3.58379835333249</v>
       </c>
       <c r="U110" t="n">
-        <v>0.272845092395748</v>
+        <v>1.42148065974604</v>
       </c>
       <c r="V110" t="n">
-        <v>10.6333333333333</v>
+        <v>1017.14834864392</v>
       </c>
       <c r="W110" t="n">
-        <v>0.352766841475279</v>
-      </c>
-      <c r="X110" t="n">
-        <v>3.58379835333249</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1.42148065974604</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>1017.14834864392</v>
-      </c>
-      <c r="AA110" t="n">
         <v>0.615432564699757</v>
       </c>
     </row>
@@ -6620,38 +4703,28 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>42508</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>100</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+        <v>0.4625</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.00478713553878167</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>0.4625</v>
+        <v>101.25</v>
       </c>
       <c r="I111" t="n">
-        <v>0.00478713553878167</v>
+        <v>7.2528729939705</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="n">
-        <v>101.25</v>
-      </c>
-      <c r="M111" t="n">
-        <v>7.2528729939705</v>
-      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
@@ -6662,10 +4735,6 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6673,48 +4742,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="n">
-        <v>100</v>
-      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>903.333333333333</v>
+      </c>
+      <c r="M112" t="n">
+        <v>11.2113533725614</v>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="n">
-        <v>903.333333333333</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>11.2113533725614</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6722,44 +4777,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>100</v>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
         <v>0.83875</v>
       </c>
-      <c r="I113" t="n">
+      <c r="E113" t="n">
         <v>0.554338945652086</v>
       </c>
+      <c r="F113" t="n">
+        <v>608.274069547608</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.155077481197304</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>608.274069547608</v>
+        <v>227.583333333333</v>
       </c>
       <c r="K113" t="n">
-        <v>0.155077481197304</v>
+        <v>0.366003187599963</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="n">
-        <v>227.583333333333</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0.366003187599963</v>
-      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
@@ -6768,10 +4813,6 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
-      <c r="Y113" t="inlineStr"/>
-      <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6779,30 +4820,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>100</v>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
         <v>0.8225</v>
       </c>
-      <c r="I114" t="n">
+      <c r="E114" t="n">
         <v>0.478713553878169</v>
       </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
@@ -6817,10 +4848,6 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6828,30 +4855,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>100</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H115" t="n">
         <v>0.875</v>
       </c>
-      <c r="I115" t="n">
+      <c r="E115" t="n">
         <v>0.288675134594814</v>
       </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
@@ -6866,10 +4883,6 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6877,40 +4890,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>100</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
         <v>0.87</v>
       </c>
-      <c r="I116" t="n">
+      <c r="E116" t="n">
         <v>0.353553390593274</v>
       </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>567.75</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1.99180613179764</v>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="n">
-        <v>567.75</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1.99180613179764</v>
-      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
@@ -6919,10 +4922,6 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6930,30 +4929,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>100</v>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H117" t="n">
         <v>0.8425</v>
       </c>
-      <c r="I117" t="n">
+      <c r="E117" t="n">
         <v>0.75</v>
       </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
@@ -6968,10 +4957,6 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6979,40 +4964,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>100</v>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
         <v>0.82</v>
       </c>
-      <c r="I118" t="n">
+      <c r="E118" t="n">
         <v>1</v>
       </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>806.666666666667</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.772801541291308</v>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="n">
-        <v>806.666666666667</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0.772801541291308</v>
-      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
@@ -7021,10 +4996,6 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7032,30 +5003,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>100</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H119" t="n">
         <v>0.745</v>
       </c>
-      <c r="I119" t="n">
+      <c r="E119" t="n">
         <v>1.6583123951777</v>
       </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
@@ -7070,10 +5031,6 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7081,40 +5038,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>100</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H120" t="n">
         <v>0.7375</v>
       </c>
-      <c r="I120" t="n">
+      <c r="E120" t="n">
         <v>0.8539125638299661</v>
       </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>1002.08333333333</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2.26729464340213</v>
+      </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="n">
-        <v>1002.08333333333</v>
-      </c>
-      <c r="O120" t="n">
-        <v>2.26729464340213</v>
-      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
@@ -7123,10 +5070,6 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
-      <c r="Y120" t="inlineStr"/>
-      <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7134,32 +5077,22 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="n">
-        <v>100</v>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="F121" t="n">
+        <v>2034.04727566223</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.46575562154142</v>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="n">
-        <v>2034.04727566223</v>
-      </c>
-      <c r="K121" t="n">
-        <v>2.46575562154142</v>
-      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
@@ -7172,10 +5105,6 @@
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
-      <c r="Y121" t="inlineStr"/>
-      <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7183,30 +5112,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>100</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
         <v>0.605</v>
       </c>
-      <c r="I122" t="n">
+      <c r="E122" t="n">
         <v>1.33853153368409</v>
       </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
@@ -7221,10 +5140,6 @@
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
-      <c r="Y122" t="inlineStr"/>
-      <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7232,7 +5147,7 @@
           <t>FAR TAS W16-06PGRNoneSeeds100CvManning</t>
         </is>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -7240,58 +5155,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>100</v>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>75.7913333333333</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1.38751448440888</v>
+      </c>
+      <c r="P123" t="n">
+        <v>12.3666666666667</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.266666666666667</v>
+      </c>
       <c r="R123" t="n">
-        <v>75.7913333333333</v>
+        <v>10.4666666666667</v>
       </c>
       <c r="S123" t="n">
-        <v>1.38751448440888</v>
+        <v>0.233333333333334</v>
       </c>
       <c r="T123" t="n">
-        <v>12.3666666666667</v>
+        <v>2.30977502647643</v>
       </c>
       <c r="U123" t="n">
-        <v>0.266666666666667</v>
+        <v>0.0940466131226932</v>
       </c>
       <c r="V123" t="n">
-        <v>10.4666666666667</v>
+        <v>983.14099865121</v>
       </c>
       <c r="W123" t="n">
-        <v>0.233333333333334</v>
-      </c>
-      <c r="X123" t="n">
-        <v>2.30977502647643</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0.0940466131226932</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>983.14099865121</v>
-      </c>
-      <c r="AA123" t="n">
         <v>0.194624815716027</v>
       </c>
     </row>
@@ -7301,38 +5202,28 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="3" t="n">
         <v>42508</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>150</v>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+        <v>0.545</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.00645497224367903</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>0.545</v>
+        <v>141.875</v>
       </c>
       <c r="I124" t="n">
-        <v>0.00645497224367903</v>
+        <v>3.28744454959573</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="n">
-        <v>141.875</v>
-      </c>
-      <c r="M124" t="n">
-        <v>3.28744454959573</v>
-      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
@@ -7343,10 +5234,6 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
-      <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7354,48 +5241,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" t="n">
-        <v>150</v>
-      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>1173.33333333333</v>
+      </c>
+      <c r="M125" t="n">
+        <v>26.8224615657185</v>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="n">
-        <v>1173.33333333333</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>26.8224615657185</v>
-      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7403,44 +5276,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>150</v>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
         <v>0.8412500000000001</v>
       </c>
-      <c r="I126" t="n">
+      <c r="E126" t="n">
         <v>0.773923984208612</v>
       </c>
+      <c r="F126" t="n">
+        <v>616.175349239404</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.32000793206631</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>616.175349239404</v>
+        <v>237.416666666667</v>
       </c>
       <c r="K126" t="n">
-        <v>0.32000793206631</v>
+        <v>0.368272996566406</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="n">
-        <v>237.416666666667</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0.368272996566406</v>
-      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
@@ -7449,10 +5312,6 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
-      <c r="Y126" t="inlineStr"/>
-      <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7460,30 +5319,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>150</v>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
         <v>0.8325</v>
       </c>
-      <c r="I127" t="n">
+      <c r="E127" t="n">
         <v>0.8539125638299661</v>
       </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
@@ -7498,10 +5347,6 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
-      <c r="Y127" t="inlineStr"/>
-      <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7509,30 +5354,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B128" s="1" t="n">
+      <c r="B128" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>150</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H128" t="n">
         <v>0.8774999999999999</v>
       </c>
-      <c r="I128" t="n">
+      <c r="E128" t="n">
         <v>0.478713553878169</v>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
@@ -7547,10 +5382,6 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
-      <c r="Y128" t="inlineStr"/>
-      <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7558,40 +5389,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B129" s="1" t="n">
+      <c r="B129" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>150</v>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
         <v>0.87125</v>
       </c>
-      <c r="I129" t="n">
+      <c r="E129" t="n">
         <v>0.239356776939085</v>
       </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>598.75</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1.91892982327824</v>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="n">
-        <v>598.75</v>
-      </c>
-      <c r="O129" t="n">
-        <v>1.91892982327824</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
@@ -7600,10 +5421,6 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
-      <c r="Y129" t="inlineStr"/>
-      <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7611,30 +5428,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B130" s="1" t="n">
+      <c r="B130" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>150</v>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
         <v>0.8525</v>
       </c>
-      <c r="I130" t="n">
+      <c r="E130" t="n">
         <v>0.250000000000001</v>
       </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
@@ -7649,10 +5456,6 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
-      <c r="Y130" t="inlineStr"/>
-      <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7660,40 +5463,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>150</v>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
         <v>0.8325</v>
       </c>
-      <c r="I131" t="n">
+      <c r="E131" t="n">
         <v>0.249999999999999</v>
       </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>810.416666666667</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.809020326622816</v>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="n">
-        <v>810.416666666667</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0.809020326622816</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
@@ -7702,10 +5495,6 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
-      <c r="Y131" t="inlineStr"/>
-      <c r="Z131" t="inlineStr"/>
-      <c r="AA131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7713,30 +5502,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B132" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>150</v>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H132" t="n">
         <v>0.7425</v>
       </c>
-      <c r="I132" t="n">
+      <c r="E132" t="n">
         <v>2.21265300789196</v>
       </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
@@ -7751,10 +5530,6 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
-      <c r="Y132" t="inlineStr"/>
-      <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7762,40 +5537,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>150</v>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
         <v>0.735</v>
       </c>
-      <c r="I133" t="n">
+      <c r="E133" t="n">
         <v>0.500000000000001</v>
       </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>1012.91666666667</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.711593803191637</v>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="n">
-        <v>1012.91666666667</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0.711593803191637</v>
-      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
@@ -7804,10 +5569,6 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
-      <c r="Y133" t="inlineStr"/>
-      <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7815,32 +5576,22 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B134" s="1" t="n">
+      <c r="B134" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C134" t="inlineStr"/>
-      <c r="D134" t="n">
-        <v>150</v>
-      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="F134" t="n">
+        <v>1830.19165948572</v>
+      </c>
+      <c r="G134" t="n">
+        <v>4.37694713543528</v>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="n">
-        <v>1830.19165948572</v>
-      </c>
-      <c r="K134" t="n">
-        <v>4.37694713543528</v>
-      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
@@ -7853,10 +5604,6 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
-      <c r="Y134" t="inlineStr"/>
-      <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7864,30 +5611,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B135" s="1" t="n">
+      <c r="B135" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>150</v>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
         <v>0.60625</v>
       </c>
-      <c r="I135" t="n">
+      <c r="E135" t="n">
         <v>1.47725815843632</v>
       </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
@@ -7902,10 +5639,6 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
-      <c r="Y135" t="inlineStr"/>
-      <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7913,7 +5646,7 @@
           <t>FAR TAS W16-06PGRNoneSeeds150CvManning</t>
         </is>
       </c>
-      <c r="B136" s="1" t="n">
+      <c r="B136" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -7921,58 +5654,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>150</v>
-      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>75.8246666666667</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1.01861692723244</v>
+      </c>
+      <c r="P136" t="n">
+        <v>12.3666666666667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.0881917103688199</v>
+      </c>
       <c r="R136" t="n">
-        <v>75.8246666666667</v>
+        <v>10.5333333333333</v>
       </c>
       <c r="S136" t="n">
-        <v>1.01861692723244</v>
+        <v>0.145296631451356</v>
       </c>
       <c r="T136" t="n">
-        <v>12.3666666666667</v>
+        <v>2.26943879168449</v>
       </c>
       <c r="U136" t="n">
-        <v>0.0881917103688199</v>
+        <v>0.0424367686531984</v>
       </c>
       <c r="V136" t="n">
-        <v>10.5333333333333</v>
+        <v>1001.53853164188</v>
       </c>
       <c r="W136" t="n">
-        <v>0.145296631451356</v>
-      </c>
-      <c r="X136" t="n">
-        <v>2.26943879168449</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0.0424367686531984</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>1001.53853164188</v>
-      </c>
-      <c r="AA136" t="n">
         <v>0.217921680617588</v>
       </c>
     </row>
@@ -7982,38 +5701,28 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B137" s="1" t="n">
+      <c r="B137" s="3" t="n">
         <v>42508</v>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>200</v>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+        <v>0.595</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.00645497224367903</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>0.595</v>
+        <v>182.5</v>
       </c>
       <c r="I137" t="n">
-        <v>0.00645497224367903</v>
+        <v>8.100925873009819</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="M137" t="n">
-        <v>8.100925873009819</v>
-      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
@@ -8024,10 +5733,6 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
-      <c r="Y137" t="inlineStr"/>
-      <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8035,48 +5740,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B138" s="1" t="n">
+      <c r="B138" s="3" t="n">
         <v>42550</v>
       </c>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="n">
-        <v>200</v>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
+      <c r="L138" t="n">
+        <v>1010</v>
+      </c>
+      <c r="M138" t="n">
+        <v>43.6844747402705</v>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="n">
-        <v>1010</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>43.6844747402705</v>
-      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8084,44 +5775,34 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B139" s="1" t="n">
+      <c r="B139" s="3" t="n">
         <v>42607</v>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>200</v>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H139" t="n">
         <v>0.8462499999999999</v>
       </c>
-      <c r="I139" t="n">
+      <c r="E139" t="n">
         <v>0.773923984208612</v>
       </c>
+      <c r="F139" t="n">
+        <v>678.287803599692</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.270604659750533</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
-        <v>678.287803599692</v>
+        <v>240.666666666667</v>
       </c>
       <c r="K139" t="n">
-        <v>0.270604659750533</v>
+        <v>0.292815198957877</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="n">
-        <v>240.666666666667</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0.292815198957877</v>
-      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
@@ -8130,10 +5811,6 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
-      <c r="Y139" t="inlineStr"/>
-      <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8141,30 +5818,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B140" s="3" t="n">
         <v>42621</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>200</v>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
         <v>0.83</v>
       </c>
-      <c r="I140" t="n">
+      <c r="E140" t="n">
         <v>0.408248290463863</v>
       </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
@@ -8179,10 +5846,6 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
-      <c r="Y140" t="inlineStr"/>
-      <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8190,30 +5853,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B141" s="1" t="n">
+      <c r="B141" s="3" t="n">
         <v>42640</v>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>200</v>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
         <v>0.875</v>
       </c>
-      <c r="I141" t="n">
+      <c r="E141" t="n">
         <v>0.500000000000001</v>
       </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
@@ -8228,10 +5881,6 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
-      <c r="Y141" t="inlineStr"/>
-      <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8239,40 +5888,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B142" s="1" t="n">
+      <c r="B142" s="3" t="n">
         <v>42650</v>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>200</v>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
         <v>0.86375</v>
       </c>
-      <c r="I142" t="n">
+      <c r="E142" t="n">
         <v>0.124999999999999</v>
       </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>573.75</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.53263117981246</v>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="n">
-        <v>573.75</v>
-      </c>
-      <c r="O142" t="n">
-        <v>1.53263117981246</v>
-      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
@@ -8281,10 +5920,6 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
-      <c r="Y142" t="inlineStr"/>
-      <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8292,30 +5927,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B143" s="1" t="n">
+      <c r="B143" s="3" t="n">
         <v>42662</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>200</v>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
         <v>0.8375</v>
       </c>
-      <c r="I143" t="n">
+      <c r="E143" t="n">
         <v>0.629152869605896</v>
       </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
@@ -8330,10 +5955,6 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
-      <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8341,40 +5962,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B144" s="3" t="n">
         <v>42676</v>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>200</v>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="I144" t="n">
+      <c r="E144" t="n">
         <v>0.288675134594814</v>
       </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>801.25</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.928895700400331</v>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="n">
-        <v>801.25</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0.928895700400331</v>
-      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
@@ -8383,10 +5994,6 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
-      <c r="Y144" t="inlineStr"/>
-      <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8394,30 +6001,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B145" s="1" t="n">
+      <c r="B145" s="3" t="n">
         <v>42689</v>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>200</v>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
         <v>0.765</v>
       </c>
-      <c r="I145" t="n">
+      <c r="E145" t="n">
         <v>1.44337567297406</v>
       </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
@@ -8432,10 +6029,6 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
-      <c r="Y145" t="inlineStr"/>
-      <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8443,40 +6036,30 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B146" s="1" t="n">
+      <c r="B146" s="3" t="n">
         <v>42696</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>200</v>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
         <v>0.7275</v>
       </c>
-      <c r="I146" t="n">
+      <c r="E146" t="n">
         <v>0.478713553878169</v>
       </c>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>1015</v>
+      </c>
+      <c r="K146" t="n">
+        <v>2.56670274144922</v>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="n">
-        <v>1015</v>
-      </c>
-      <c r="O146" t="n">
-        <v>2.56670274144922</v>
-      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
@@ -8485,10 +6068,6 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
-      <c r="Y146" t="inlineStr"/>
-      <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8496,32 +6075,22 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B147" s="1" t="n">
+      <c r="B147" s="3" t="n">
         <v>42698</v>
       </c>
       <c r="C147" t="inlineStr"/>
-      <c r="D147" t="n">
-        <v>200</v>
-      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="F147" t="n">
+        <v>1866.37819224826</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3.26146275080291</v>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="n">
-        <v>1866.37819224826</v>
-      </c>
-      <c r="K147" t="n">
-        <v>3.26146275080291</v>
-      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -8534,10 +6103,6 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
-      <c r="Y147" t="inlineStr"/>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8545,30 +6110,20 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B148" s="1" t="n">
+      <c r="B148" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>200</v>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
         <v>0.57375</v>
       </c>
-      <c r="I148" t="n">
+      <c r="E148" t="n">
         <v>1.54616460960662</v>
       </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
@@ -8583,10 +6138,6 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
-      <c r="Y148" t="inlineStr"/>
-      <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8594,7 +6145,7 @@
           <t>FAR TAS W16-06PGRNoneSeeds200CvManning</t>
         </is>
       </c>
-      <c r="B149" s="1" t="n">
+      <c r="B149" s="3" t="n">
         <v>42752</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -8602,58 +6153,44 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>200</v>
-      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Manning</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
+      <c r="N149" t="n">
+        <v>76.35599999999999</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1.04980760142037</v>
+      </c>
+      <c r="P149" t="n">
+        <v>12.6333333333333</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0.4371625682868</v>
+      </c>
       <c r="R149" t="n">
-        <v>76.35599999999999</v>
+        <v>10.3</v>
       </c>
       <c r="S149" t="n">
-        <v>1.04980760142037</v>
+        <v>0.173205080756888</v>
       </c>
       <c r="T149" t="n">
-        <v>12.6333333333333</v>
+        <v>2.04478706586433</v>
       </c>
       <c r="U149" t="n">
-        <v>0.4371625682868</v>
+        <v>0.0324904883154109</v>
       </c>
       <c r="V149" t="n">
-        <v>10.3</v>
+        <v>934.335954587708</v>
       </c>
       <c r="W149" t="n">
-        <v>0.173205080756888</v>
-      </c>
-      <c r="X149" t="n">
-        <v>2.04478706586433</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>0.0324904883154109</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>934.335954587708</v>
-      </c>
-      <c r="AA149" t="n">
         <v>0.276407348256313</v>
       </c>
     </row>
